--- a/Configs/GameConfig/Datas/Buff.xlsx
+++ b/Configs/GameConfig/Datas/Buff.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21310" windowHeight="16860"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="基础Buff表" sheetId="1" r:id="rId1"/>
+    <sheet name="基础状态表" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,64 +28,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>d</t>
-    </r>
-  </si>
-  <si>
-    <t>sub_id</t>
+    <t>id</t>
   </si>
   <si>
     <t>name</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>d</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>esc</t>
-    </r>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>mian_item_id</t>
-  </si>
-  <si>
-    <t>reward_list</t>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>buff_type</t>
+  </si>
+  <si>
+    <t>target_type</t>
+  </si>
+  <si>
+    <t>trigger_type</t>
+  </si>
+  <si>
+    <t>status_id</t>
+  </si>
+  <si>
+    <t>value_params</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>tick_interval</t>
+  </si>
+  <si>
+    <t>max_stacks</t>
   </si>
   <si>
     <t>##type</t>
@@ -96,111 +75,145 @@
     <t>string</t>
   </si>
   <si>
-    <t>int#ref=item.TbItem</t>
-  </si>
-  <si>
-    <t>(list#sep=;),int#ref=item.TbItem</t>
+    <t>EBuffType</t>
+  </si>
+  <si>
+    <t>ETargetType</t>
+  </si>
+  <si>
+    <t>ETriggerType</t>
+  </si>
+  <si>
+    <t>int#ref=battle.TbStatus</t>
+  </si>
+  <si>
+    <t>(list#sep=;),float</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <t>##group</t>
   </si>
   <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>这是i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-      </rPr>
-      <t>d</t>
-    </r>
-  </si>
-  <si>
-    <t>这是子id</t>
-  </si>
-  <si>
-    <t>名字</t>
+    <t>BuffID</t>
+  </si>
+  <si>
+    <t>名称</t>
   </si>
   <si>
     <t>描述</t>
   </si>
   <si>
-    <t>价格</t>
-  </si>
-  <si>
-    <t>主奖励</t>
-  </si>
-  <si>
-    <t>奖励1</t>
-  </si>
-  <si>
-    <t>10001;10002</t>
-  </si>
-  <si>
-    <t>奖励2</t>
-  </si>
-  <si>
-    <t>10001;10003</t>
-  </si>
-  <si>
-    <t>奖励3</t>
-  </si>
-  <si>
-    <t>10001;10004</t>
-  </si>
-  <si>
-    <t>奖励4</t>
-  </si>
-  <si>
-    <t>10001;10005</t>
-  </si>
-  <si>
-    <t>奖励5</t>
-  </si>
-  <si>
-    <t>10001;10006</t>
-  </si>
-  <si>
-    <t>奖励6</t>
-  </si>
-  <si>
-    <t>10001;10007</t>
-  </si>
-  <si>
-    <t>奖励7</t>
-  </si>
-  <si>
-    <t>10001;10008</t>
-  </si>
-  <si>
-    <t>奖励8</t>
-  </si>
-  <si>
-    <t>10001;10009</t>
-  </si>
-  <si>
-    <t>奖励9</t>
-  </si>
-  <si>
-    <t>奖励10</t>
+    <t>Buff类型</t>
+  </si>
+  <si>
+    <t>作用目标</t>
+  </si>
+  <si>
+    <t>触发类型</t>
+  </si>
+  <si>
+    <t>状态ID</t>
+  </si>
+  <si>
+    <t>数值参数</t>
+  </si>
+  <si>
+    <t>持续时间</t>
+  </si>
+  <si>
+    <t>触发间隔</t>
+  </si>
+  <si>
+    <t>最大叠加层数</t>
+  </si>
+  <si>
+    <t>攻击强化</t>
+  </si>
+  <si>
+    <t>提升攻击力</t>
+  </si>
+  <si>
+    <t>PropertyMod</t>
+  </si>
+  <si>
+    <t>Friendly</t>
+  </si>
+  <si>
+    <t>Immediate</t>
+  </si>
+  <si>
+    <t>治疗光环</t>
+  </si>
+  <si>
+    <t>持续治疗友军</t>
+  </si>
+  <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>中毒</t>
+  </si>
+  <si>
+    <t>持续受到伤害</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>眩晕</t>
+  </si>
+  <si>
+    <t>使目标无法行动</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>击退</t>
+  </si>
+  <si>
+    <t>30%概率击退敌人</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>can_move</t>
+  </si>
+  <si>
+    <t>can_attack</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>all</t>
+  </si>
+  <si>
+    <t>状态名</t>
+  </si>
+  <si>
+    <t>能否移动</t>
+  </si>
+  <si>
+    <t>能否攻击</t>
+  </si>
+  <si>
+    <t>减速</t>
+  </si>
+  <si>
+    <t>沉默</t>
   </si>
 </sst>
 </file>
@@ -229,6 +242,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -236,15 +255,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -391,7 +403,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,18 +448,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -597,7 +597,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -626,21 +626,6 @@
       </left>
       <right style="thin">
         <color rgb="FFC6C6C6"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFC6C6C6"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -760,19 +745,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -781,7 +766,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -793,119 +778,119 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -917,41 +902,32 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1301,402 +1277,470 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.29090909090909" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.71818181818182" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.4363636363636" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.0090909090909" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.4363636363636" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.57272727272727" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26" style="2" customWidth="1"/>
+    <col min="3" max="3" width="37.7272727272727" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.0909090909091" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7272727272727" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.8181818181818" style="2" customWidth="1"/>
     <col min="7" max="7" width="32.5727272727273" style="2" customWidth="1"/>
-    <col min="8" max="8" width="48.1454545454545" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1454545454545" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.4363636363636" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.8636363636364" style="1" customWidth="1"/>
-    <col min="12" max="12" width="28.0090909090909" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.0090909090909" style="3" customWidth="1"/>
-    <col min="14" max="14" width="5.14545454545455" style="3" customWidth="1"/>
-    <col min="15" max="36" width="12.4363636363636" style="1" customWidth="1"/>
+    <col min="8" max="8" width="27.8181818181818" style="1" customWidth="1"/>
+    <col min="9" max="9" width="34.5454545454545" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.8636363636364" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.1818181818182" style="1" customWidth="1"/>
+    <col min="12" max="12" width="13.0090909090909" style="3" customWidth="1"/>
+    <col min="13" max="34" width="12.4363636363636" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" spans="1:15">
-      <c r="A1" s="4" t="s">
+    <row r="1" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="11"/>
-    </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:15">
-      <c r="A2" s="6" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="6"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2"/>
+      <c r="C2"/>
+      <c r="D2"/>
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2" s="7"/>
+      <c r="I2"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="6"/>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" spans="1:13">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="6"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1" spans="1:13">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4" s="4"/>
+      <c r="I4"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" ht="20.25" customHeight="1" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B6" s="11">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>20</v>
+      </c>
+      <c r="J6" s="1">
         <v>10</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="11"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1" spans="1:15">
-      <c r="A3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="6" t="s">
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="L6" s="12"/>
+    </row>
+    <row r="7" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B7" s="11">
+        <v>2</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>50</v>
+      </c>
+      <c r="J7" s="1">
+        <v>20</v>
+      </c>
+      <c r="K7" s="1">
+        <v>2</v>
+      </c>
+      <c r="L7" s="12"/>
+    </row>
+    <row r="8" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B8" s="11">
+        <v>3</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
         <v>15</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="12"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:15">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="11"/>
-    </row>
-    <row r="5" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B5" s="8">
+      <c r="K8" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="8">
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B9" s="11">
+        <v>4</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="8">
-        <v>100</v>
-      </c>
-      <c r="G5" s="8">
-        <v>10001</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-    </row>
-    <row r="6" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B6" s="8">
-        <v>2</v>
-      </c>
-      <c r="C6" s="8">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="8">
-        <v>100</v>
-      </c>
-      <c r="G6" s="8">
-        <v>10002</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-    </row>
-    <row r="7" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B7" s="8">
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="8">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="8">
-        <v>100</v>
-      </c>
-      <c r="G7" s="8">
-        <v>10003</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-    </row>
-    <row r="8" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B8" s="8">
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" ht="20.25" customHeight="1" spans="1:13">
+      <c r="B10" s="11">
+        <v>5</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10" s="1">
         <v>4</v>
       </c>
-      <c r="C8" s="8">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="8">
-        <v>100</v>
-      </c>
-      <c r="G8" s="8">
-        <v>10004</v>
-      </c>
-      <c r="H8" s="1" t="s">
+      <c r="I10" s="1">
         <v>30</v>
       </c>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-    </row>
-    <row r="9" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B9" s="8">
-        <v>5</v>
-      </c>
-      <c r="C9" s="8">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="8">
-        <v>100</v>
-      </c>
-      <c r="G9" s="8">
-        <v>10005</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16"/>
-    </row>
-    <row r="10" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B10" s="8">
-        <v>6</v>
-      </c>
-      <c r="C10" s="8">
-        <v>6</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="8">
-        <v>100</v>
-      </c>
-      <c r="G10" s="8">
-        <v>10006</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-    </row>
-    <row r="11" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B11" s="8">
-        <v>7</v>
-      </c>
-      <c r="C11" s="8">
-        <v>7</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="8">
-        <v>100</v>
-      </c>
-      <c r="G11" s="8">
-        <v>10007</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-    </row>
-    <row r="12" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B12" s="8">
-        <v>8</v>
-      </c>
-      <c r="C12" s="8">
-        <v>8</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="8">
-        <v>200</v>
-      </c>
-      <c r="G12" s="8">
-        <v>10008</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-    </row>
-    <row r="13" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B13" s="8">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>9</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="8">
-        <v>300</v>
-      </c>
-      <c r="G13" s="8">
-        <v>10009</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-    </row>
-    <row r="14" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B14" s="8">
-        <v>10</v>
-      </c>
-      <c r="C14" s="8">
-        <v>10</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="8">
-        <v>100</v>
-      </c>
-      <c r="G14" s="8">
-        <v>10000</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
+      <c r="L10" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="M2:N2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="41.0909090909091" customWidth="1"/>
+    <col min="3" max="3" width="25.3636363636364" customWidth="1"/>
+    <col min="4" max="4" width="45.1818181818182" customWidth="1"/>
+    <col min="5" max="5" width="67.7272727272727" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="29.8181818181818" customWidth="1"/>
+    <col min="8" max="8" width="53.9090909090909" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Configs/GameConfig/Datas/Buff.xlsx
+++ b/Configs/GameConfig/Datas/Buff.xlsx
@@ -42,7 +42,7 @@
     <t>desc</t>
   </si>
   <si>
-    <t>buff_type</t>
+    <t>buff_effects</t>
   </si>
   <si>
     <t>target_type</t>
@@ -54,7 +54,10 @@
     <t>status_id</t>
   </si>
   <si>
-    <t>value_params</t>
+    <t>target_params</t>
+  </si>
+  <si>
+    <t>condition_params</t>
   </si>
   <si>
     <t>duration</t>
@@ -75,7 +78,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>EBuffType</t>
+    <t>(list#sep=;),(CBuffEffect#sep=,)</t>
   </si>
   <si>
     <t>ETargetType</t>
@@ -108,7 +111,7 @@
     <t>描述</t>
   </si>
   <si>
-    <t>Buff类型</t>
+    <t>Buff效果</t>
   </si>
   <si>
     <t>作用目标</t>
@@ -120,7 +123,10 @@
     <t>状态ID</t>
   </si>
   <si>
-    <t>数值参数</t>
+    <t>目标参数</t>
+  </si>
+  <si>
+    <t>触发参数</t>
   </si>
   <si>
     <t>持续时间</t>
@@ -138,7 +144,7 @@
     <t>提升攻击力</t>
   </si>
   <si>
-    <t>PropertyMod</t>
+    <t>Damage,1;</t>
   </si>
   <si>
     <t>Friendly</t>
@@ -153,7 +159,7 @@
     <t>持续治疗友军</t>
   </si>
   <si>
-    <t>Heal</t>
+    <t>Heal,1</t>
   </si>
   <si>
     <t>Interval</t>
@@ -165,9 +171,6 @@
     <t>持续受到伤害</t>
   </si>
   <si>
-    <t>Damage</t>
-  </si>
-  <si>
     <t>Enemy</t>
   </si>
   <si>
@@ -177,7 +180,7 @@
     <t>使目标无法行动</t>
   </si>
   <si>
-    <t>Status</t>
+    <t>Status,1</t>
   </si>
   <si>
     <t>击退</t>
@@ -196,9 +199,6 @@
   </si>
   <si>
     <t>bool</t>
-  </si>
-  <si>
-    <t>all</t>
   </si>
   <si>
     <t>状态名</t>
@@ -890,7 +890,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -902,6 +902,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -909,6 +912,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1277,25 +1283,24 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9.29090909090909" style="1" customWidth="1"/>
     <col min="2" max="2" width="26" style="2" customWidth="1"/>
     <col min="3" max="3" width="37.7272727272727" style="1" customWidth="1"/>
     <col min="4" max="4" width="24.0909090909091" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7272727272727" style="1" customWidth="1"/>
+    <col min="5" max="5" width="47.1818181818182" style="1" customWidth="1"/>
     <col min="6" max="6" width="26.8181818181818" style="2" customWidth="1"/>
     <col min="7" max="7" width="32.5727272727273" style="2" customWidth="1"/>
-    <col min="8" max="8" width="27.8181818181818" style="1" customWidth="1"/>
-    <col min="9" max="9" width="34.5454545454545" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.8636363636364" style="1" customWidth="1"/>
-    <col min="11" max="11" width="19.1818181818182" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.0090909090909" style="3" customWidth="1"/>
-    <col min="13" max="34" width="12.4363636363636" style="1" customWidth="1"/>
+    <col min="8" max="10" width="27.8181818181818" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.8636363636364" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.1818181818182" style="1" customWidth="1"/>
+    <col min="13" max="13" width="13.0090909090909" style="3" customWidth="1"/>
+    <col min="14" max="35" width="12.4363636363636" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" spans="1:13">
+    <row r="1" ht="21.75" customHeight="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1320,21 +1325,24 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:13">
+      <c r="M1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="7"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1" spans="1:14">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1344,55 +1352,59 @@
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2"/>
-      <c r="H2" s="7"/>
-      <c r="I2"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="6"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1" spans="1:13">
+      <c r="H2" s="8"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="7"/>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" spans="1:14">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" s="6"/>
-    </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:13">
+      <c r="N3" s="7"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1" spans="1:14">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4"/>
       <c r="C4"/>
@@ -1401,208 +1413,227 @@
       <c r="F4"/>
       <c r="G4"/>
       <c r="H4" s="4"/>
-      <c r="I4"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="6"/>
-    </row>
-    <row r="5" ht="20.25" customHeight="1" spans="1:13">
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="7"/>
+    </row>
+    <row r="5" ht="20.25" customHeight="1" spans="1:14">
       <c r="A5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="B5" s="13" t="s">
         <v>24</v>
       </c>
+      <c r="C5" s="13" t="s">
+        <v>25</v>
+      </c>
       <c r="D5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="F5" s="13" t="s">
         <v>28</v>
       </c>
+      <c r="G5" s="13" t="s">
+        <v>29</v>
+      </c>
       <c r="H5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="12" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="6" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B6" s="11">
+      <c r="L5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="20.25" customHeight="1" spans="1:14">
+      <c r="B6" s="13">
         <v>1</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>34</v>
+      <c r="C6" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="11" t="s">
         <v>38</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
       </c>
       <c r="I6" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
         <v>10</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>0</v>
       </c>
-      <c r="L6" s="12"/>
-    </row>
-    <row r="7" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B7" s="11">
+      <c r="M6" s="14"/>
+    </row>
+    <row r="7" ht="20.25" customHeight="1" spans="1:14">
+      <c r="B7" s="13">
         <v>2</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>42</v>
+      <c r="G7" s="13" t="s">
+        <v>44</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
       </c>
       <c r="I7" s="1">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="J7" s="1">
+        <v>2</v>
+      </c>
+      <c r="K7" s="1">
         <v>20</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>2</v>
       </c>
-      <c r="L7" s="12"/>
-    </row>
-    <row r="8" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B8" s="11">
+      <c r="M7" s="14"/>
+    </row>
+    <row r="8" ht="20.25" customHeight="1" spans="1:14">
+      <c r="B8" s="13">
         <v>3</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>43</v>
+      <c r="C8" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>44</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>42</v>
       </c>
       <c r="H8" s="1">
         <v>0</v>
       </c>
       <c r="I8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="1">
+        <v>3</v>
+      </c>
+      <c r="K8" s="1">
         <v>15</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>1</v>
       </c>
-      <c r="L8" s="12"/>
-    </row>
-    <row r="9" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B9" s="11">
+      <c r="M8" s="14"/>
+    </row>
+    <row r="9" ht="20.25" customHeight="1" spans="1:14">
+      <c r="B9" s="13">
         <v>4</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>38</v>
+      <c r="G9" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
       <c r="I9" s="1">
+        <v>3</v>
+      </c>
+      <c r="J9" s="1">
+        <v>4</v>
+      </c>
+      <c r="K9" s="1">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1">
         <v>0</v>
       </c>
-      <c r="J9" s="1">
-        <v>3</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-      <c r="L9" s="12"/>
-    </row>
-    <row r="10" ht="20.25" customHeight="1" spans="1:13">
-      <c r="B10" s="11">
+      <c r="M9" s="14"/>
+    </row>
+    <row r="10" ht="20.25" customHeight="1" spans="1:14">
+      <c r="B10" s="13">
         <v>5</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>52</v>
+      <c r="F10" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>53</v>
       </c>
       <c r="H10" s="1">
         <v>4</v>
       </c>
       <c r="I10" s="1">
-        <v>30</v>
-      </c>
-      <c r="L10" s="12"/>
+        <v>4</v>
+      </c>
+      <c r="J10" s="1">
+        <v>5</v>
+      </c>
+      <c r="M10" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1636,10 +1667,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1649,41 +1680,32 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>57</v>
@@ -1700,7 +1722,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1733,7 +1755,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>

--- a/Configs/GameConfig/Datas/Buff.xlsx
+++ b/Configs/GameConfig/Datas/Buff.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="63">
   <si>
     <t>##var</t>
   </si>
@@ -138,37 +138,40 @@
     <t>最大叠加层数</t>
   </si>
   <si>
-    <t>攻击强化</t>
-  </si>
-  <si>
-    <t>提升攻击力</t>
+    <t>造成伤害</t>
+  </si>
+  <si>
+    <t>造成10点物理伤害</t>
+  </si>
+  <si>
+    <t>Damage,Physical,10;</t>
+  </si>
+  <si>
+    <t>Friendly</t>
+  </si>
+  <si>
+    <t>Immediate</t>
+  </si>
+  <si>
+    <t>治疗光环</t>
+  </si>
+  <si>
+    <t>持续治疗友军</t>
+  </si>
+  <si>
+    <t>Heal,None,1</t>
+  </si>
+  <si>
+    <t>Interval</t>
+  </si>
+  <si>
+    <t>中毒</t>
+  </si>
+  <si>
+    <t>持续受到伤害</t>
   </si>
   <si>
     <t>Damage,1;</t>
-  </si>
-  <si>
-    <t>Friendly</t>
-  </si>
-  <si>
-    <t>Immediate</t>
-  </si>
-  <si>
-    <t>治疗光环</t>
-  </si>
-  <si>
-    <t>持续治疗友军</t>
-  </si>
-  <si>
-    <t>Heal,1</t>
-  </si>
-  <si>
-    <t>Interval</t>
-  </si>
-  <si>
-    <t>中毒</t>
-  </si>
-  <si>
-    <t>持续受到伤害</t>
   </si>
   <si>
     <t>Enemy</t>
@@ -1465,7 +1468,7 @@
       <c r="B6" s="13">
         <v>1</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="15" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -1544,10 +1547,10 @@
         <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" s="13" t="s">
         <v>44</v>
@@ -1574,16 +1577,16 @@
         <v>4</v>
       </c>
       <c r="C9" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>48</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>40</v>
@@ -1610,19 +1613,19 @@
         <v>5</v>
       </c>
       <c r="C10" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="F10" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H10" s="1">
         <v>4</v>
@@ -1667,10 +1670,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -1689,10 +1692,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1708,13 +1711,13 @@
         <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1722,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1730,7 +1733,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -1744,7 +1747,7 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -1755,7 +1758,7 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
